--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Indonesia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/TTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4094A35-0900-7246-A521-8ADB1F92E3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F7AD5D-5AA4-414E-97FF-82D31AF87BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" firstSheet="10" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -3035,7 +3035,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3307,6 +3307,13 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3834,7 +3841,7 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3918,6 +3925,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="88">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -7537,13 +7545,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -7671,8 +7679,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7800,8 +7868,88 @@
         <f>'EV Sales Share'!AH2</f>
         <v>0.42299999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0.44146451612903093</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0.4552556451612908</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0.46904677419354712</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0.482837903225807</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0.49662903225806332</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0.51042016129032319</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0.52421129032257952</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0.53800241935483939</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0.55179354838709571</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0.56558467741935559</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0.57937580645161191</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0.59316693548387178</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0.6069580645161281</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0.62074919354838798</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0.6345403225806443</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0.64833145161290417</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0.6621225806451605</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0.67591370967742037</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0.68970483870967669</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0.70349596774193657</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7929,8 +8077,88 @@
         <f>Data!AL11</f>
         <v>1.2259779596081354E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>1.3765958881985091E-3</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>1.4121537648702776E-3</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>1.447711641542046E-3</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>1.4832695182138145E-3</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>1.5188273948855968E-3</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>1.5543852715573653E-3</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>1.5899431482291337E-3</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>1.6255010249009022E-3</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>1.6610589015726707E-3</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>1.6966167782444391E-3</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>1.7321746549162076E-3</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>1.7677325315879761E-3</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>1.8032904082597445E-3</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>1.838848284931513E-3</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>1.8744061616032814E-3</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>1.9099640382750499E-3</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>1.9455219149468322E-3</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>1.9810797916186007E-3</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>2.0166376682903692E-3</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>2.0521955449621376E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -8058,8 +8286,88 @@
         <f>Data!AL12</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8187,8 +8495,88 @@
         <f>Data!AL13</f>
         <v>3.0818463927506423E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>3.1705284170691295E-2</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>3.2592104413876166E-2</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>3.347892465706126E-2</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>3.4365744900246131E-2</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>3.5252565143431003E-2</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>3.6139385386615874E-2</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>3.7026205629800968E-2</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>3.7913025872985839E-2</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>3.8799846116170711E-2</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>3.9686666359355804E-2</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>4.0573486602540676E-2</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>4.1460306845725547E-2</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>4.2347127088910641E-2</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>4.3233947332095513E-2</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>4.4120767575280384E-2</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>4.5007587818465478E-2</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>4.5894408061650349E-2</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>4.6781228304835221E-2</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>4.7668048548020314E-2</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>4.8554868791205186E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8316,8 +8704,88 @@
         <f>Data!AL14</f>
         <v>0.32773377328321535</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0.39778782460026818</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0.40505317297535726</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0.41231852135044633</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0.41958386972553541</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0.42684921810062271</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0.43411456647571178</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0.44137991485080086</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0.44864526322588993</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0.45591061160097723</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0.46317595997606631</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0.47044130835115539</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0.47770665672624446</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0.48497200510133354</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0.49223735347642084</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0.49950270185150991</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0.50676805022659899</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0.51403339860168806</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0.52129874697677536</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0.52856409535186444</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0.53582944372695351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -8445,8 +8913,88 @@
         <f>Data!AL15</f>
         <v>8.6165104068937348E-4</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>8.7975251645557029E-4</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>8.9785399222177403E-4</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>9.1595546798797084E-4</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>9.3405694375416765E-4</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>9.5215841952036445E-4</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>9.7025989528656126E-4</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>9.8836137105275806E-4</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>1.0064628468189549E-3</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>1.0245643225851586E-3</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>1.0426657983513554E-3</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>1.0607672741175522E-3</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>1.078868749883749E-3</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>1.0969702256499458E-3</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>1.1150717014161426E-3</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>1.1331731771823395E-3</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>1.1512746529485432E-3</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>1.16937612871474E-3</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>1.1874776044809368E-3</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>1.2055790802471336E-3</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>1.2236805560133304E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -8573,6 +9121,86 @@
       <c r="AF8">
         <f>Data!AL16</f>
         <v>3.1168958329050089E-4</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>3.6193428069642569E-4</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>3.7379604755572587E-4</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>3.8565781441502953E-4</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>3.9751958127433318E-4</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>4.0938134813363683E-4</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>4.2124311499294048E-4</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>4.3310488185224413E-4</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>4.4496664871154779E-4</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>4.5682841557085144E-4</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>4.6869018243015162E-4</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>4.8055194928945527E-4</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>4.9241371614875892E-4</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>5.0427548300806257E-4</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>5.1613724986736623E-4</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>5.2799901672666988E-4</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>5.3986078358597353E-4</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>5.5172255044527718E-4</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>5.6358431730457736E-4</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>5.7544608416388102E-4</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
+        <v>5.8730785102318467E-4</v>
       </c>
     </row>
   </sheetData>
@@ -8585,13 +9213,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -8719,8 +9347,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8848,8 +9536,88 @@
         <f>Data!AL17</f>
         <v>0.9999999881542101</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>AF2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8977,8 +9745,88 @@
         <f>Data!AL18</f>
         <v>1.235369525889815E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>1.2351562279764002E-3</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>1.2349429300629856E-3</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>1.2347296321495709E-3</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>1.2345163342361565E-3</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>1.2343030363227421E-3</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>1.2340897384093275E-3</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>1.2338764404959128E-3</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>1.2336631425824984E-3</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>1.233449844669084E-3</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>1.2332365467556694E-3</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>1.2330232488422547E-3</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>1.2328099509288403E-3</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>1.2325966530154259E-3</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>1.2323833551020113E-3</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>1.2321700571885966E-3</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>1.2319567592751822E-3</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AH2:AZ8" si="2">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>1.2317434613617678E-3</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="2"/>
+        <v>1.2315301634483532E-3</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="2"/>
+        <v>1.2313168655349385E-3</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="2"/>
+        <v>1.2311035676215241E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -9106,8 +9954,88 @@
         <f>Data!AL19</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -9235,8 +10163,88 @@
         <f>Data!AL20</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -9364,8 +10372,88 @@
         <f>Data!AL21</f>
         <v>0.32413298494392645</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0.38188095235825514</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="2"/>
+        <v>0.39551409100636903</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="2"/>
+        <v>0.40914722965447936</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="2"/>
+        <v>0.42278036830259325</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="2"/>
+        <v>0.43641350695070358</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="2"/>
+        <v>0.45004664559881746</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="2"/>
+        <v>0.46367978424693135</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="2"/>
+        <v>0.47731292289504168</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="2"/>
+        <v>0.49094606154315557</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="2"/>
+        <v>0.50457920019126945</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="2"/>
+        <v>0.51821233883937978</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="2"/>
+        <v>0.53184547748749367</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="2"/>
+        <v>0.545478616135604</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="2"/>
+        <v>0.55911175478371788</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="2"/>
+        <v>0.57274489343183177</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="2"/>
+        <v>0.5863780320799421</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="2"/>
+        <v>0.60001117072805599</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="2"/>
+        <v>0.61364430937616987</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="2"/>
+        <v>0.6272774480242802</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="2"/>
+        <v>0.64091058667239409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -9493,8 +10581,88 @@
         <f>Data!AL22</f>
         <v>8.6165104068937001E-4</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>8.7532986991119277E-4</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="2"/>
+        <v>8.8900869913301206E-4</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="2"/>
+        <v>9.0268752835483135E-4</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="2"/>
+        <v>9.1636635757665064E-4</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="2"/>
+        <v>9.3004518679846993E-4</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="2"/>
+        <v>9.4372401602029268E-4</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="2"/>
+        <v>9.5740284524211197E-4</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="2"/>
+        <v>9.7108167446393126E-4</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="2"/>
+        <v>9.8476050368575055E-4</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="2"/>
+        <v>9.9843933290757331E-4</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="2"/>
+        <v>1.0121181621293926E-3</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="2"/>
+        <v>1.0257969913512119E-3</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="2"/>
+        <v>1.0394758205730312E-3</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="2"/>
+        <v>1.0531546497948505E-3</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="2"/>
+        <v>1.0668334790166732E-3</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="2"/>
+        <v>1.0805123082384925E-3</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="2"/>
+        <v>1.0941911374603118E-3</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="2"/>
+        <v>1.1078699666821311E-3</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="2"/>
+        <v>1.1215487959039504E-3</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="2"/>
+        <v>1.1352276251257731E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -9621,6 +10789,86 @@
       <c r="AF8">
         <f>Data!AL23</f>
         <v>3.1136358282645159E-4</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>3.6683653642968425E-4</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="2"/>
+        <v>3.7993258987632783E-4</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="2"/>
+        <v>3.9302864332297141E-4</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="2"/>
+        <v>4.0612469676961846E-4</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="2"/>
+        <v>4.1922075021626204E-4</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="2"/>
+        <v>4.3231680366290562E-4</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="2"/>
+        <v>4.4541285710955267E-4</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="2"/>
+        <v>4.5850891055619625E-4</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="2"/>
+        <v>4.7160496400283983E-4</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="2"/>
+        <v>4.8470101744948341E-4</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="2"/>
+        <v>4.9779707089613046E-4</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="2"/>
+        <v>5.1089312434277404E-4</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="2"/>
+        <v>5.2398917778941762E-4</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="2"/>
+        <v>5.3708523123606466E-4</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="2"/>
+        <v>5.5018128468270824E-4</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="2"/>
+        <v>5.6327733812935182E-4</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="2"/>
+        <v>5.763733915759954E-4</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="2"/>
+        <v>5.8946944502264245E-4</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="2"/>
+        <v>6.0256549846928603E-4</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="2"/>
+        <v>6.1566155191592961E-4</v>
       </c>
     </row>
   </sheetData>
@@ -9633,13 +10881,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -9767,8 +11015,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1" s="51">
+        <v>2051</v>
+      </c>
+      <c r="AH1" s="51">
+        <v>2052</v>
+      </c>
+      <c r="AI1" s="51">
+        <v>2053</v>
+      </c>
+      <c r="AJ1" s="51">
+        <v>2054</v>
+      </c>
+      <c r="AK1" s="51">
+        <v>2055</v>
+      </c>
+      <c r="AL1" s="51">
+        <v>2056</v>
+      </c>
+      <c r="AM1" s="51">
+        <v>2057</v>
+      </c>
+      <c r="AN1" s="51">
+        <v>2058</v>
+      </c>
+      <c r="AO1" s="51">
+        <v>2059</v>
+      </c>
+      <c r="AP1" s="51">
+        <v>2060</v>
+      </c>
+      <c r="AQ1" s="51">
+        <v>2061</v>
+      </c>
+      <c r="AR1" s="51">
+        <v>2062</v>
+      </c>
+      <c r="AS1" s="51">
+        <v>2063</v>
+      </c>
+      <c r="AT1" s="51">
+        <v>2064</v>
+      </c>
+      <c r="AU1" s="51">
+        <v>2065</v>
+      </c>
+      <c r="AV1" s="51">
+        <v>2066</v>
+      </c>
+      <c r="AW1" s="51">
+        <v>2067</v>
+      </c>
+      <c r="AX1" s="51">
+        <v>2068</v>
+      </c>
+      <c r="AY1" s="51">
+        <v>2069</v>
+      </c>
+      <c r="AZ1" s="51">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -9896,8 +11204,88 @@
         <f>Data!AL24</f>
         <v>0.9999999881542101</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2" s="51">
+        <f>AF2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AH2" s="51">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AI2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AJ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AK2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AL2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AM2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AN2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AO2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AP2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AQ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AR2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AS2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AT2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AU2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AV2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AW2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AX2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AY2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AZ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10025,8 +11413,68 @@
         <f>Data!AL25</f>
         <v>0.16005020400931197</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3" s="51">
+        <v>1.377E-3</v>
+      </c>
+      <c r="AH3" s="51">
+        <v>1.4120000000000001E-3</v>
+      </c>
+      <c r="AI3" s="51">
+        <v>1.4480000000000001E-3</v>
+      </c>
+      <c r="AJ3" s="51">
+        <v>1.4829999999999999E-3</v>
+      </c>
+      <c r="AK3" s="51">
+        <v>1.519E-3</v>
+      </c>
+      <c r="AL3" s="51">
+        <v>1.554E-3</v>
+      </c>
+      <c r="AM3" s="51">
+        <v>1.5900000000000001E-3</v>
+      </c>
+      <c r="AN3" s="51">
+        <v>1.6260000000000001E-3</v>
+      </c>
+      <c r="AO3" s="51">
+        <v>1.6609999999999999E-3</v>
+      </c>
+      <c r="AP3" s="51">
+        <v>1.6969999999999999E-3</v>
+      </c>
+      <c r="AQ3" s="51">
+        <v>1.732E-3</v>
+      </c>
+      <c r="AR3" s="51">
+        <v>1.768E-3</v>
+      </c>
+      <c r="AS3" s="51">
+        <v>1.8029999999999999E-3</v>
+      </c>
+      <c r="AT3" s="51">
+        <v>1.8389999999999999E-3</v>
+      </c>
+      <c r="AU3" s="51">
+        <v>1.874E-3</v>
+      </c>
+      <c r="AV3" s="51">
+        <v>1.91E-3</v>
+      </c>
+      <c r="AW3" s="51">
+        <v>1.946E-3</v>
+      </c>
+      <c r="AX3" s="51">
+        <v>1.9810000000000001E-3</v>
+      </c>
+      <c r="AY3" s="51">
+        <v>2.0170000000000001E-3</v>
+      </c>
+      <c r="AZ3" s="51">
+        <v>2.052E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10154,8 +11602,68 @@
         <f>Data!AL26</f>
         <v>0.29946959893376196</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AH4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AI4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AJ4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AL4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AN4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AO4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AP4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AQ4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AR4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AS4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AT4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AU4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AV4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AW4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AX4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AY4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AZ4" s="51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10283,8 +11791,88 @@
         <f>Data!AL27</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5" s="51">
+        <f>AF5</f>
+        <v>3</v>
+      </c>
+      <c r="AH5" s="51">
+        <f t="shared" ref="AH5:AZ5" si="1">AG5</f>
+        <v>3</v>
+      </c>
+      <c r="AI5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AJ5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AK5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AL5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AM5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AN5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AO5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AP5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AQ5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AR5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AS5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AT5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AU5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AV5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AW5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AX5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AY5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AZ5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10412,8 +12000,68 @@
         <f>Data!AL28</f>
         <v>8.18920096381031E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6" s="51">
+        <v>0.39778799999999997</v>
+      </c>
+      <c r="AH6" s="51">
+        <v>0.405053</v>
+      </c>
+      <c r="AI6" s="51">
+        <v>0.41231899999999999</v>
+      </c>
+      <c r="AJ6" s="51">
+        <v>0.41958400000000001</v>
+      </c>
+      <c r="AK6" s="51">
+        <v>0.42684899999999998</v>
+      </c>
+      <c r="AL6" s="51">
+        <v>0.43411499999999997</v>
+      </c>
+      <c r="AM6" s="51">
+        <v>0.44137999999999999</v>
+      </c>
+      <c r="AN6" s="51">
+        <v>0.44864500000000002</v>
+      </c>
+      <c r="AO6" s="51">
+        <v>0.45591100000000001</v>
+      </c>
+      <c r="AP6" s="51">
+        <v>0.46317599999999998</v>
+      </c>
+      <c r="AQ6" s="51">
+        <v>0.470441</v>
+      </c>
+      <c r="AR6" s="51">
+        <v>0.47770699999999999</v>
+      </c>
+      <c r="AS6" s="51">
+        <v>0.48497200000000001</v>
+      </c>
+      <c r="AT6" s="51">
+        <v>0.49223699999999998</v>
+      </c>
+      <c r="AU6" s="51">
+        <v>0.49950299999999997</v>
+      </c>
+      <c r="AV6" s="51">
+        <v>0.506768</v>
+      </c>
+      <c r="AW6" s="51">
+        <v>0.51403299999999996</v>
+      </c>
+      <c r="AX6" s="51">
+        <v>0.52129899999999996</v>
+      </c>
+      <c r="AY6" s="51">
+        <v>0.52856400000000003</v>
+      </c>
+      <c r="AZ6" s="51">
+        <v>0.535829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -10541,8 +12189,68 @@
         <f>Data!AL29</f>
         <v>0.51993486392741062</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="51">
+        <v>8.8000000000000003E-4</v>
+      </c>
+      <c r="AH7" s="51">
+        <v>8.9800000000000004E-4</v>
+      </c>
+      <c r="AI7" s="51">
+        <v>9.1600000000000004E-4</v>
+      </c>
+      <c r="AJ7" s="51">
+        <v>9.3400000000000004E-4</v>
+      </c>
+      <c r="AK7" s="51">
+        <v>9.5200000000000005E-4</v>
+      </c>
+      <c r="AL7" s="51">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="AM7" s="51">
+        <v>9.8799999999999995E-4</v>
+      </c>
+      <c r="AN7" s="51">
+        <v>1.0059999999999999E-3</v>
+      </c>
+      <c r="AO7" s="51">
+        <v>1.0250000000000001E-3</v>
+      </c>
+      <c r="AP7" s="51">
+        <v>1.0430000000000001E-3</v>
+      </c>
+      <c r="AQ7" s="51">
+        <v>1.0610000000000001E-3</v>
+      </c>
+      <c r="AR7" s="51">
+        <v>1.0790000000000001E-3</v>
+      </c>
+      <c r="AS7" s="51">
+        <v>1.0970000000000001E-3</v>
+      </c>
+      <c r="AT7" s="51">
+        <v>1.1150000000000001E-3</v>
+      </c>
+      <c r="AU7" s="51">
+        <v>1.1329999999999999E-3</v>
+      </c>
+      <c r="AV7" s="51">
+        <v>1.1509999999999999E-3</v>
+      </c>
+      <c r="AW7" s="51">
+        <v>1.1689999999999999E-3</v>
+      </c>
+      <c r="AX7" s="51">
+        <v>1.1869999999999999E-3</v>
+      </c>
+      <c r="AY7" s="51">
+        <v>1.206E-3</v>
+      </c>
+      <c r="AZ7" s="51">
+        <v>1.224E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -10669,6 +12377,66 @@
       <c r="AF8">
         <f>Data!AL30</f>
         <v>0.17108784051909381</v>
+      </c>
+      <c r="AG8" s="51">
+        <v>3.6200000000000002E-4</v>
+      </c>
+      <c r="AH8" s="51">
+        <v>3.7399999999999998E-4</v>
+      </c>
+      <c r="AI8" s="51">
+        <v>3.86E-4</v>
+      </c>
+      <c r="AJ8" s="51">
+        <v>3.9800000000000002E-4</v>
+      </c>
+      <c r="AK8" s="51">
+        <v>4.0900000000000002E-4</v>
+      </c>
+      <c r="AL8" s="51">
+        <v>4.2099999999999999E-4</v>
+      </c>
+      <c r="AM8" s="51">
+        <v>4.3300000000000001E-4</v>
+      </c>
+      <c r="AN8" s="51">
+        <v>4.4499999999999997E-4</v>
+      </c>
+      <c r="AO8" s="51">
+        <v>4.57E-4</v>
+      </c>
+      <c r="AP8" s="51">
+        <v>4.6900000000000002E-4</v>
+      </c>
+      <c r="AQ8" s="51">
+        <v>4.8099999999999998E-4</v>
+      </c>
+      <c r="AR8" s="51">
+        <v>4.9200000000000003E-4</v>
+      </c>
+      <c r="AS8" s="51">
+        <v>5.04E-4</v>
+      </c>
+      <c r="AT8" s="51">
+        <v>5.1599999999999997E-4</v>
+      </c>
+      <c r="AU8" s="51">
+        <v>5.2800000000000004E-4</v>
+      </c>
+      <c r="AV8" s="51">
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="AW8" s="51">
+        <v>5.5199999999999997E-4</v>
+      </c>
+      <c r="AX8" s="51">
+        <v>5.6400000000000005E-4</v>
+      </c>
+      <c r="AY8" s="51">
+        <v>5.7499999999999999E-4</v>
+      </c>
+      <c r="AZ8" s="51">
+        <v>5.8699999999999996E-4</v>
       </c>
     </row>
   </sheetData>
@@ -10681,13 +12449,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -10815,8 +12583,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1" s="51">
+        <v>2051</v>
+      </c>
+      <c r="AH1" s="51">
+        <v>2052</v>
+      </c>
+      <c r="AI1" s="51">
+        <v>2053</v>
+      </c>
+      <c r="AJ1" s="51">
+        <v>2054</v>
+      </c>
+      <c r="AK1" s="51">
+        <v>2055</v>
+      </c>
+      <c r="AL1" s="51">
+        <v>2056</v>
+      </c>
+      <c r="AM1" s="51">
+        <v>2057</v>
+      </c>
+      <c r="AN1" s="51">
+        <v>2058</v>
+      </c>
+      <c r="AO1" s="51">
+        <v>2059</v>
+      </c>
+      <c r="AP1" s="51">
+        <v>2060</v>
+      </c>
+      <c r="AQ1" s="51">
+        <v>2061</v>
+      </c>
+      <c r="AR1" s="51">
+        <v>2062</v>
+      </c>
+      <c r="AS1" s="51">
+        <v>2063</v>
+      </c>
+      <c r="AT1" s="51">
+        <v>2064</v>
+      </c>
+      <c r="AU1" s="51">
+        <v>2065</v>
+      </c>
+      <c r="AV1" s="51">
+        <v>2066</v>
+      </c>
+      <c r="AW1" s="51">
+        <v>2067</v>
+      </c>
+      <c r="AX1" s="51">
+        <v>2068</v>
+      </c>
+      <c r="AY1" s="51">
+        <v>2069</v>
+      </c>
+      <c r="AZ1" s="51">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10944,8 +12772,88 @@
         <f>Data!AL31</f>
         <v>0.9999999881542101</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2" s="51">
+        <f>AF2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AH2" s="51">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AI2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AJ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AK2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AL2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AM2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AN2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AO2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AP2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AQ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AR2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AS2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AT2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AU2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AV2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AW2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AX2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AY2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AZ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11073,8 +12981,68 @@
         <f>Data!AL32</f>
         <v>5.2333311909740617E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3" s="51">
+        <v>1.377E-3</v>
+      </c>
+      <c r="AH3" s="51">
+        <v>1.4120000000000001E-3</v>
+      </c>
+      <c r="AI3" s="51">
+        <v>1.4480000000000001E-3</v>
+      </c>
+      <c r="AJ3" s="51">
+        <v>1.4829999999999999E-3</v>
+      </c>
+      <c r="AK3" s="51">
+        <v>1.519E-3</v>
+      </c>
+      <c r="AL3" s="51">
+        <v>1.554E-3</v>
+      </c>
+      <c r="AM3" s="51">
+        <v>1.5900000000000001E-3</v>
+      </c>
+      <c r="AN3" s="51">
+        <v>1.6260000000000001E-3</v>
+      </c>
+      <c r="AO3" s="51">
+        <v>1.6609999999999999E-3</v>
+      </c>
+      <c r="AP3" s="51">
+        <v>1.6969999999999999E-3</v>
+      </c>
+      <c r="AQ3" s="51">
+        <v>1.732E-3</v>
+      </c>
+      <c r="AR3" s="51">
+        <v>1.768E-3</v>
+      </c>
+      <c r="AS3" s="51">
+        <v>1.8029999999999999E-3</v>
+      </c>
+      <c r="AT3" s="51">
+        <v>1.8389999999999999E-3</v>
+      </c>
+      <c r="AU3" s="51">
+        <v>1.874E-3</v>
+      </c>
+      <c r="AV3" s="51">
+        <v>1.91E-3</v>
+      </c>
+      <c r="AW3" s="51">
+        <v>1.946E-3</v>
+      </c>
+      <c r="AX3" s="51">
+        <v>1.9810000000000001E-3</v>
+      </c>
+      <c r="AY3" s="51">
+        <v>2.0170000000000001E-3</v>
+      </c>
+      <c r="AZ3" s="51">
+        <v>2.052E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11202,8 +13170,88 @@
         <f>Data!AL33</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4" s="51">
+        <f>AF4</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="51">
+        <f t="shared" ref="AH4:AZ4" si="1">AG4</f>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11331,8 +13379,88 @@
         <f>Data!AL34</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5" s="51">
+        <f>AF5</f>
+        <v>5</v>
+      </c>
+      <c r="AH5" s="51">
+        <f t="shared" ref="AH5:AZ5" si="2">AG5</f>
+        <v>5</v>
+      </c>
+      <c r="AI5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AJ5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AK5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AL5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AM5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AN5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AO5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AP5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AQ5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AR5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AS5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AT5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AU5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AV5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AW5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AX5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AY5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AZ5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -11460,8 +13588,68 @@
         <f>Data!AL35</f>
         <v>2.7321073384308624E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6" s="51">
+        <v>0.39778799999999997</v>
+      </c>
+      <c r="AH6" s="51">
+        <v>0.405053</v>
+      </c>
+      <c r="AI6" s="51">
+        <v>0.41231899999999999</v>
+      </c>
+      <c r="AJ6" s="51">
+        <v>0.41958400000000001</v>
+      </c>
+      <c r="AK6" s="51">
+        <v>0.42684899999999998</v>
+      </c>
+      <c r="AL6" s="51">
+        <v>0.43411499999999997</v>
+      </c>
+      <c r="AM6" s="51">
+        <v>0.44137999999999999</v>
+      </c>
+      <c r="AN6" s="51">
+        <v>0.44864500000000002</v>
+      </c>
+      <c r="AO6" s="51">
+        <v>0.45591100000000001</v>
+      </c>
+      <c r="AP6" s="51">
+        <v>0.46317599999999998</v>
+      </c>
+      <c r="AQ6" s="51">
+        <v>0.470441</v>
+      </c>
+      <c r="AR6" s="51">
+        <v>0.47770699999999999</v>
+      </c>
+      <c r="AS6" s="51">
+        <v>0.48497200000000001</v>
+      </c>
+      <c r="AT6" s="51">
+        <v>0.49223699999999998</v>
+      </c>
+      <c r="AU6" s="51">
+        <v>0.49950299999999997</v>
+      </c>
+      <c r="AV6" s="51">
+        <v>0.506768</v>
+      </c>
+      <c r="AW6" s="51">
+        <v>0.51403299999999996</v>
+      </c>
+      <c r="AX6" s="51">
+        <v>0.52129899999999996</v>
+      </c>
+      <c r="AY6" s="51">
+        <v>0.52856400000000003</v>
+      </c>
+      <c r="AZ6" s="51">
+        <v>0.535829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -11589,8 +13777,68 @@
         <f>Data!AL36</f>
         <v>6.1785980743152003E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="51">
+        <v>8.8000000000000003E-4</v>
+      </c>
+      <c r="AH7" s="51">
+        <v>8.9800000000000004E-4</v>
+      </c>
+      <c r="AI7" s="51">
+        <v>9.1600000000000004E-4</v>
+      </c>
+      <c r="AJ7" s="51">
+        <v>9.3400000000000004E-4</v>
+      </c>
+      <c r="AK7" s="51">
+        <v>9.5200000000000005E-4</v>
+      </c>
+      <c r="AL7" s="51">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="AM7" s="51">
+        <v>9.8799999999999995E-4</v>
+      </c>
+      <c r="AN7" s="51">
+        <v>1.0059999999999999E-3</v>
+      </c>
+      <c r="AO7" s="51">
+        <v>1.0250000000000001E-3</v>
+      </c>
+      <c r="AP7" s="51">
+        <v>1.0430000000000001E-3</v>
+      </c>
+      <c r="AQ7" s="51">
+        <v>1.0610000000000001E-3</v>
+      </c>
+      <c r="AR7" s="51">
+        <v>1.0790000000000001E-3</v>
+      </c>
+      <c r="AS7" s="51">
+        <v>1.0970000000000001E-3</v>
+      </c>
+      <c r="AT7" s="51">
+        <v>1.1150000000000001E-3</v>
+      </c>
+      <c r="AU7" s="51">
+        <v>1.1329999999999999E-3</v>
+      </c>
+      <c r="AV7" s="51">
+        <v>1.1509999999999999E-3</v>
+      </c>
+      <c r="AW7" s="51">
+        <v>1.1689999999999999E-3</v>
+      </c>
+      <c r="AX7" s="51">
+        <v>1.1869999999999999E-3</v>
+      </c>
+      <c r="AY7" s="51">
+        <v>1.206E-3</v>
+      </c>
+      <c r="AZ7" s="51">
+        <v>1.224E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -11717,6 +13965,66 @@
       <c r="AF8">
         <f>Data!AL37</f>
         <v>6.0995164686396177E-3</v>
+      </c>
+      <c r="AG8" s="51">
+        <v>3.6200000000000002E-4</v>
+      </c>
+      <c r="AH8" s="51">
+        <v>3.7399999999999998E-4</v>
+      </c>
+      <c r="AI8" s="51">
+        <v>3.86E-4</v>
+      </c>
+      <c r="AJ8" s="51">
+        <v>3.9800000000000002E-4</v>
+      </c>
+      <c r="AK8" s="51">
+        <v>4.0900000000000002E-4</v>
+      </c>
+      <c r="AL8" s="51">
+        <v>4.2099999999999999E-4</v>
+      </c>
+      <c r="AM8" s="51">
+        <v>4.3300000000000001E-4</v>
+      </c>
+      <c r="AN8" s="51">
+        <v>4.4499999999999997E-4</v>
+      </c>
+      <c r="AO8" s="51">
+        <v>4.57E-4</v>
+      </c>
+      <c r="AP8" s="51">
+        <v>4.6900000000000002E-4</v>
+      </c>
+      <c r="AQ8" s="51">
+        <v>4.8099999999999998E-4</v>
+      </c>
+      <c r="AR8" s="51">
+        <v>4.9200000000000003E-4</v>
+      </c>
+      <c r="AS8" s="51">
+        <v>5.04E-4</v>
+      </c>
+      <c r="AT8" s="51">
+        <v>5.1599999999999997E-4</v>
+      </c>
+      <c r="AU8" s="51">
+        <v>5.2800000000000004E-4</v>
+      </c>
+      <c r="AV8" s="51">
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="AW8" s="51">
+        <v>5.5199999999999997E-4</v>
+      </c>
+      <c r="AX8" s="51">
+        <v>5.6400000000000005E-4</v>
+      </c>
+      <c r="AY8" s="51">
+        <v>5.7499999999999999E-4</v>
+      </c>
+      <c r="AZ8" s="51">
+        <v>5.8699999999999996E-4</v>
       </c>
     </row>
   </sheetData>
@@ -11729,13 +14037,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -11863,8 +14171,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11992,8 +14360,88 @@
         <f>Data!AL38</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12121,8 +14569,88 @@
         <f>Data!AL39</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12250,8 +14778,88 @@
         <f>Data!AL40</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12379,8 +14987,88 @@
         <f>Data!AL41</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12508,8 +15196,88 @@
         <f>Data!AL42</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -12637,8 +15405,88 @@
         <f>Data!AL43</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -12764,6 +15612,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL44</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -12777,13 +15705,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -12911,8 +15839,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13040,8 +16028,88 @@
         <f>Data!AL45</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13169,8 +16237,88 @@
         <f>Data!AL46</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13298,8 +16446,88 @@
         <f>Data!AL47</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13427,8 +16655,88 @@
         <f>Data!AL48</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13556,8 +16864,88 @@
         <f>Data!AL49</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -13685,8 +17073,88 @@
         <f>Data!AL50</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -13812,6 +17280,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL51</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -13825,13 +17373,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -13959,8 +17507,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14088,8 +17696,68 @@
         <f>Data!AL52</f>
         <v>0.99727709808185716</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14217,8 +17885,88 @@
         <f>Data!AL53</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="0">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AH2:AZ8" si="1">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14346,8 +18094,88 @@
         <f>Data!AL54</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -14475,8 +18303,68 @@
         <f>Data!AL55</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14604,8 +18492,88 @@
         <f>Data!AL56</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -14733,8 +18701,88 @@
         <f>Data!AL57</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -14860,6 +18908,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL58</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -14873,13 +19001,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -15007,8 +19135,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15136,8 +19324,88 @@
         <f>Data!AL59</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15265,8 +19533,88 @@
         <f>Data!AL60</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -15394,8 +19742,88 @@
         <f>Data!AL61</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -15523,8 +19951,88 @@
         <f>Data!AL62</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15652,8 +20160,88 @@
         <f>Data!AL63</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -15781,8 +20369,88 @@
         <f>Data!AL64</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -15908,6 +20576,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL65</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15921,13 +20669,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -16055,8 +20803,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16184,8 +20992,88 @@
         <f>Data!AL66</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16313,8 +21201,88 @@
         <f>Data!AL67</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -16442,8 +21410,88 @@
         <f>Data!AL68</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -16571,8 +21619,88 @@
         <f>Data!AL69</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -16700,8 +21828,88 @@
         <f>Data!AL70</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -16829,8 +22037,88 @@
         <f>Data!AL71</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -16956,6 +22244,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL72</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -23313,13 +28681,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -23447,8 +28815,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -23576,8 +29004,88 @@
         <f>Data!AL73</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -23705,8 +29213,88 @@
         <f>Data!AL74</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -23834,8 +29422,88 @@
         <f>Data!AL75</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -23963,8 +29631,88 @@
         <f>Data!AL76</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -24092,8 +29840,88 @@
         <f>Data!AL77</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -24221,8 +30049,88 @@
         <f>Data!AL78</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -24348,6 +30256,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL79</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -24361,13 +30349,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -24495,8 +30483,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -24624,8 +30672,88 @@
         <f>Data!AL80</f>
         <v>0.99999998753074737</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>AF2</f>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -24753,8 +30881,88 @@
         <f>Data!AL81</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AH2:AZ8" si="2">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -24882,8 +31090,88 @@
         <f>Data!AL82</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -25011,8 +31299,88 @@
         <f>Data!AL83</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -25140,8 +31508,88 @@
         <f>Data!AL84</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -25269,8 +31717,88 @@
         <f>Data!AL85</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -25396,6 +31924,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL86</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -25409,13 +32017,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -25543,8 +32151,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -25641,8 +32309,88 @@
       <c r="AF2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -25739,8 +32487,88 @@
       <c r="AF3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -25837,8 +32665,88 @@
       <c r="AF4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -25935,8 +32843,88 @@
       <c r="AF5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -26033,8 +33021,88 @@
       <c r="AF6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -26131,8 +33199,88 @@
       <c r="AF7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -26227,6 +33375,86 @@
         <v>1</v>
       </c>
       <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/TTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F7AD5D-5AA4-414E-97FF-82D31AF87BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFEE66E-0F44-4E46-B37C-D9706D50C850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" firstSheet="10" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="780" windowWidth="32340" windowHeight="21360" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <sheet name="TTS-motorbikes-psgr" sheetId="17" r:id="rId21"/>
     <sheet name="TTS-motorbikes-frgt" sheetId="18" r:id="rId22"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -9810,7 +9810,7 @@
         <v>1.2319567592751822E-3</v>
       </c>
       <c r="AW3">
-        <f t="shared" ref="AH2:AZ8" si="2">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <f t="shared" ref="AH3:AZ8" si="2">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
         <v>1.2317434613617678E-3</v>
       </c>
       <c r="AX3">
@@ -17950,7 +17950,7 @@
         <v>0</v>
       </c>
       <c r="AW3">
-        <f t="shared" ref="AH2:AZ8" si="1">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <f t="shared" ref="AH3:AZ8" si="1">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
         <v>0</v>
       </c>
       <c r="AX3">
@@ -30946,7 +30946,7 @@
         <v>0</v>
       </c>
       <c r="AW3">
-        <f t="shared" ref="AH2:AZ8" si="2">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <f t="shared" ref="AH3:AZ8" si="2">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
         <v>0</v>
       </c>
       <c r="AX3">
@@ -30968,207 +30968,207 @@
       </c>
       <c r="B4">
         <f>Data!H82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <f>Data!I82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <f>Data!J82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Data!K82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>Data!L82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <f>Data!M82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <f>Data!N82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <f>Data!O82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <f>Data!P82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f>Data!Q82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <f>Data!R82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <f>Data!S82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <f>Data!T82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O4">
         <f>Data!U82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <f>Data!V82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <f>Data!W82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <f>Data!X82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4">
         <f>Data!Y82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <f>Data!Z82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4">
         <f>Data!AA82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V4">
         <f>Data!AB82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4">
         <f>Data!AC82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X4">
         <f>Data!AD82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <f>Data!AE82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z4">
         <f>Data!AF82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA4">
         <f>Data!AG82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB4">
         <f>Data!AH82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC4">
         <f>Data!AI82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD4">
         <f>Data!AJ82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE4">
         <f>Data!AK82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <f>Data!AL82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG4">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.2">
@@ -76018,10 +76018,10 @@
         <v>3</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82" s="7" t="str">
         <f>IF(D82=E82,"n/a",IF(OR(C82="battery electric vehicle",C82="natural gas vehicle",C82="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -76029,127 +76029,127 @@
       </c>
       <c r="H82" s="22">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,I$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,J$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,K$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,L$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,M$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,N$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,O$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,P$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,Q$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,R$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,S$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,T$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,U$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,V$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,W$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,X$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,Y$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,Z$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AA$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AB$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AC$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AD$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AE$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AF$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AG$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AH$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AI$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AJ$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AK$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AL$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.2">

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/TTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFEE66E-0F44-4E46-B37C-D9706D50C850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A414894-BBDA-5E47-82E8-4D7AF9D8115B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="780" windowWidth="32340" windowHeight="21360" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -5009,6 +5009,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5016,7 +5017,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -75738,7 +75738,6 @@
         <v>1</v>
       </c>
       <c r="D80" s="22">
-        <f>'SYVbT-passenger'!C6/SUM('SYVbT-passenger'!6:6)</f>
         <v>0</v>
       </c>
       <c r="E80">
